--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188942</v>
+        <v>113187238</v>
       </c>
       <c r="B15" t="n">
-        <v>89993</v>
+        <v>90029</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,25 +2128,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685000</v>
+        <v>685022</v>
       </c>
       <c r="R15" t="n">
-        <v>7024832</v>
+        <v>7024825</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2207,19 +2207,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113187238</v>
+        <v>113189203</v>
       </c>
       <c r="B16" t="n">
         <v>90029</v>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685022</v>
+        <v>685051</v>
       </c>
       <c r="R16" t="n">
-        <v>7024825</v>
+        <v>7024861</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2293,9 +2293,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,22 +2320,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113189203</v>
+        <v>113188942</v>
       </c>
       <c r="B17" t="n">
-        <v>90029</v>
+        <v>89993</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2334,25 +2344,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2373,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685051</v>
+        <v>685000</v>
       </c>
       <c r="R17" t="n">
-        <v>7024861</v>
+        <v>7024832</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2396,19 +2406,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2423,12 +2423,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113184104</v>
       </c>
       <c r="B2" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>113184262</v>
       </c>
       <c r="B3" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113187255</v>
+        <v>113186913</v>
       </c>
       <c r="B4" t="n">
-        <v>90469</v>
+        <v>90059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684984</v>
+        <v>685111</v>
       </c>
       <c r="R4" t="n">
-        <v>7024863</v>
+        <v>7024849</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113187010</v>
+        <v>113189203</v>
       </c>
       <c r="B5" t="n">
-        <v>56910</v>
+        <v>90045</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,40 +1024,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
+          <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685101</v>
+        <v>685051</v>
       </c>
       <c r="R5" t="n">
-        <v>7024816</v>
+        <v>7024861</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1089,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,12 +1109,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1244,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113189038</v>
+        <v>113189210</v>
       </c>
       <c r="B7" t="n">
-        <v>97298</v>
+        <v>90009</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,32 +1251,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1289,13 +1280,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685017</v>
+        <v>685061</v>
       </c>
       <c r="R7" t="n">
-        <v>7024837</v>
+        <v>7024867</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,19 +1313,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1330,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113189059</v>
+        <v>113188210</v>
       </c>
       <c r="B8" t="n">
-        <v>89993</v>
+        <v>78121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,25 +1354,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,13 +1383,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685035</v>
+        <v>684969</v>
       </c>
       <c r="R8" t="n">
-        <v>7024859</v>
+        <v>7024861</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,9 +1416,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1443,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188210</v>
+        <v>113186700</v>
       </c>
       <c r="B9" t="n">
-        <v>78105</v>
+        <v>90045</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1471,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684969</v>
+        <v>685137</v>
       </c>
       <c r="R9" t="n">
-        <v>7024861</v>
+        <v>7024870</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,19 +1529,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,22 +1546,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188009</v>
+        <v>113189059</v>
       </c>
       <c r="B10" t="n">
-        <v>97298</v>
+        <v>90009</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,32 +1570,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,13 +1599,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685000</v>
+        <v>685035</v>
       </c>
       <c r="R10" t="n">
-        <v>7024858</v>
+        <v>7024859</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1655,19 +1632,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,22 +1649,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113186700</v>
+        <v>113187373</v>
       </c>
       <c r="B11" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685137</v>
+        <v>685080</v>
       </c>
       <c r="R11" t="n">
-        <v>7024870</v>
+        <v>7024880</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1785,22 +1752,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113186856</v>
+        <v>113187255</v>
       </c>
       <c r="B12" t="n">
-        <v>90029</v>
+        <v>90485</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1776,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1838,13 +1805,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685107</v>
+        <v>684984</v>
       </c>
       <c r="R12" t="n">
-        <v>7024929</v>
+        <v>7024863</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1871,19 +1838,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,22 +1855,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113186695</v>
+        <v>113188942</v>
       </c>
       <c r="B13" t="n">
-        <v>90469</v>
+        <v>90009</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,25 +1879,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685137</v>
+        <v>685000</v>
       </c>
       <c r="R13" t="n">
-        <v>7024870</v>
+        <v>7024832</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2001,22 +1958,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113186913</v>
+        <v>113189289</v>
       </c>
       <c r="B14" t="n">
-        <v>90043</v>
+        <v>90045</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685111</v>
+        <v>685096</v>
       </c>
       <c r="R14" t="n">
-        <v>7024849</v>
+        <v>7024930</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2116,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113187238</v>
+        <v>113188009</v>
       </c>
       <c r="B15" t="n">
-        <v>90029</v>
+        <v>97314</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,28 +2085,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2157,13 +2118,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685022</v>
+        <v>685000</v>
       </c>
       <c r="R15" t="n">
-        <v>7024825</v>
+        <v>7024858</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2190,9 +2151,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,22 +2178,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113189203</v>
+        <v>113187010</v>
       </c>
       <c r="B16" t="n">
-        <v>90029</v>
+        <v>56910</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,35 +2206,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bredtomyran (Bredtomyran), Ång</t>
+          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685051</v>
+        <v>685101</v>
       </c>
       <c r="R16" t="n">
-        <v>7024861</v>
+        <v>7024816</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2295,7 +2271,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,7 +2281,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,22 +2296,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188942</v>
+        <v>113187126</v>
       </c>
       <c r="B17" t="n">
-        <v>89993</v>
+        <v>90059</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2344,25 +2320,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2373,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685000</v>
+        <v>685103</v>
       </c>
       <c r="R17" t="n">
-        <v>7024832</v>
+        <v>7024817</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2435,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188157</v>
+        <v>113187238</v>
       </c>
       <c r="B18" t="n">
-        <v>56781</v>
+        <v>90045</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2451,21 +2427,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2476,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684971</v>
+        <v>685022</v>
       </c>
       <c r="R18" t="n">
-        <v>7024844</v>
+        <v>7024825</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2538,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113189210</v>
+        <v>113188157</v>
       </c>
       <c r="B19" t="n">
-        <v>89993</v>
+        <v>56781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2550,25 +2526,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2579,10 +2555,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685061</v>
+        <v>684971</v>
       </c>
       <c r="R19" t="n">
-        <v>7024867</v>
+        <v>7024844</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2641,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113189289</v>
+        <v>113186856</v>
       </c>
       <c r="B20" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,13 +2658,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685096</v>
+        <v>685107</v>
       </c>
       <c r="R20" t="n">
-        <v>7024930</v>
+        <v>7024929</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2715,9 +2691,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,22 +2718,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113187373</v>
+        <v>113187338</v>
       </c>
       <c r="B21" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,7 +2774,7 @@
         <v>685080</v>
       </c>
       <c r="R21" t="n">
-        <v>7024880</v>
+        <v>7024876</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2847,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113187338</v>
+        <v>113189038</v>
       </c>
       <c r="B22" t="n">
-        <v>90029</v>
+        <v>97314</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2859,28 +2845,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2888,13 +2878,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685080</v>
+        <v>685017</v>
       </c>
       <c r="R22" t="n">
-        <v>7024876</v>
+        <v>7024837</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2921,9 +2911,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,22 +2938,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113187126</v>
+        <v>113186695</v>
       </c>
       <c r="B23" t="n">
-        <v>90043</v>
+        <v>90485</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,25 +2962,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685103</v>
+        <v>685137</v>
       </c>
       <c r="R23" t="n">
-        <v>7024817</v>
+        <v>7024870</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3041,12 +3041,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3056,7 +3056,7 @@
         <v>113187692</v>
       </c>
       <c r="B24" t="n">
-        <v>89975</v>
+        <v>89991</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113184104</v>
+        <v>113184262</v>
       </c>
       <c r="B2" t="n">
-        <v>97314</v>
+        <v>90045</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -720,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685031</v>
+        <v>685072</v>
       </c>
       <c r="R2" t="n">
-        <v>7024817</v>
+        <v>7024868</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113184262</v>
+        <v>113184104</v>
       </c>
       <c r="B3" t="n">
-        <v>90045</v>
+        <v>97314</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,28 +800,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685072</v>
+        <v>685031</v>
       </c>
       <c r="R3" t="n">
-        <v>7024868</v>
+        <v>7024817</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113186913</v>
+        <v>113186700</v>
       </c>
       <c r="B4" t="n">
-        <v>90059</v>
+        <v>90045</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685111</v>
+        <v>685137</v>
       </c>
       <c r="R4" t="n">
-        <v>7024849</v>
+        <v>7024870</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113189203</v>
+        <v>113187181</v>
       </c>
       <c r="B5" t="n">
-        <v>90045</v>
+        <v>56781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,35 +1024,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685051</v>
+        <v>685052</v>
       </c>
       <c r="R5" t="n">
-        <v>7024861</v>
+        <v>7024833</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,22 +1114,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113187181</v>
+        <v>113186856</v>
       </c>
       <c r="B6" t="n">
-        <v>56781</v>
+        <v>90045</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,40 +1142,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685052</v>
+        <v>685107</v>
       </c>
       <c r="R6" t="n">
-        <v>7024833</v>
+        <v>7024929</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113189210</v>
+        <v>113186695</v>
       </c>
       <c r="B7" t="n">
-        <v>90009</v>
+        <v>90485</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,25 +1251,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685061</v>
+        <v>685137</v>
       </c>
       <c r="R7" t="n">
-        <v>7024867</v>
+        <v>7024870</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113186700</v>
+        <v>113187010</v>
       </c>
       <c r="B9" t="n">
-        <v>90045</v>
+        <v>56910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,38 +1471,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bredtomyran (Bredtomyran), Ång</t>
+          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685137</v>
+        <v>685101</v>
       </c>
       <c r="R9" t="n">
-        <v>7024870</v>
+        <v>7024816</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,9 +1534,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,22 +1561,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113189059</v>
+        <v>113187126</v>
       </c>
       <c r="B10" t="n">
-        <v>90009</v>
+        <v>90059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,25 +1585,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685035</v>
+        <v>685103</v>
       </c>
       <c r="R10" t="n">
-        <v>7024859</v>
+        <v>7024817</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1649,22 +1664,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113187373</v>
+        <v>113189210</v>
       </c>
       <c r="B11" t="n">
-        <v>90045</v>
+        <v>90009</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,25 +1688,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1702,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685080</v>
+        <v>685061</v>
       </c>
       <c r="R11" t="n">
-        <v>7024880</v>
+        <v>7024867</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1752,22 +1767,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113187255</v>
+        <v>113189289</v>
       </c>
       <c r="B12" t="n">
-        <v>90485</v>
+        <v>90045</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,25 +1791,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684984</v>
+        <v>685096</v>
       </c>
       <c r="R12" t="n">
-        <v>7024863</v>
+        <v>7024930</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1867,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188942</v>
+        <v>113187338</v>
       </c>
       <c r="B13" t="n">
-        <v>90009</v>
+        <v>90045</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,25 +1894,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1908,10 +1923,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685000</v>
+        <v>685080</v>
       </c>
       <c r="R13" t="n">
-        <v>7024832</v>
+        <v>7024876</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1970,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113189289</v>
+        <v>113189038</v>
       </c>
       <c r="B14" t="n">
-        <v>90045</v>
+        <v>97314</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,28 +1997,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2011,13 +2030,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685096</v>
+        <v>685017</v>
       </c>
       <c r="R14" t="n">
-        <v>7024930</v>
+        <v>7024837</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,9 +2063,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,22 +2090,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188009</v>
+        <v>113189203</v>
       </c>
       <c r="B15" t="n">
-        <v>97314</v>
+        <v>90045</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,32 +2114,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2118,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685000</v>
+        <v>685051</v>
       </c>
       <c r="R15" t="n">
-        <v>7024858</v>
+        <v>7024861</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2153,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2163,7 +2188,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,22 +2203,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113187010</v>
+        <v>113188942</v>
       </c>
       <c r="B16" t="n">
-        <v>56910</v>
+        <v>90009</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,47 +2227,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
+          <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685101</v>
+        <v>685000</v>
       </c>
       <c r="R16" t="n">
-        <v>7024816</v>
+        <v>7024832</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2269,19 +2289,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2296,22 +2306,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113187126</v>
+        <v>113187373</v>
       </c>
       <c r="B17" t="n">
-        <v>90059</v>
+        <v>90045</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2324,21 +2334,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2349,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685103</v>
+        <v>685080</v>
       </c>
       <c r="R17" t="n">
-        <v>7024817</v>
+        <v>7024880</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2411,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113187238</v>
+        <v>113188157</v>
       </c>
       <c r="B18" t="n">
-        <v>90045</v>
+        <v>56781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685022</v>
+        <v>684971</v>
       </c>
       <c r="R18" t="n">
-        <v>7024825</v>
+        <v>7024844</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2514,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188157</v>
+        <v>113188009</v>
       </c>
       <c r="B19" t="n">
-        <v>56781</v>
+        <v>97314</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2526,28 +2536,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2555,13 +2569,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684971</v>
+        <v>685000</v>
       </c>
       <c r="R19" t="n">
-        <v>7024844</v>
+        <v>7024858</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2588,9 +2602,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,22 +2629,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113186856</v>
+        <v>113186913</v>
       </c>
       <c r="B20" t="n">
-        <v>90045</v>
+        <v>90059</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2633,21 +2657,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,13 +2682,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685107</v>
+        <v>685111</v>
       </c>
       <c r="R20" t="n">
-        <v>7024929</v>
+        <v>7024849</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2691,19 +2715,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,19 +2732,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113187338</v>
+        <v>113187238</v>
       </c>
       <c r="B21" t="n">
         <v>90045</v>
@@ -2771,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685080</v>
+        <v>685022</v>
       </c>
       <c r="R21" t="n">
-        <v>7024876</v>
+        <v>7024825</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2821,22 +2835,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113189038</v>
+        <v>113189059</v>
       </c>
       <c r="B22" t="n">
-        <v>97314</v>
+        <v>90009</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2845,32 +2859,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2878,13 +2888,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685017</v>
+        <v>685035</v>
       </c>
       <c r="R22" t="n">
-        <v>7024837</v>
+        <v>7024859</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2911,19 +2921,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,19 +2938,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113186695</v>
+        <v>113187255</v>
       </c>
       <c r="B23" t="n">
         <v>90485</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685137</v>
+        <v>684984</v>
       </c>
       <c r="R23" t="n">
-        <v>7024870</v>
+        <v>7024863</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113184262</v>
       </c>
       <c r="B2" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>113184104</v>
       </c>
       <c r="B3" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113186700</v>
+        <v>113188009</v>
       </c>
       <c r="B4" t="n">
-        <v>90045</v>
+        <v>97326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,28 +917,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685137</v>
+        <v>685000</v>
       </c>
       <c r="R4" t="n">
-        <v>7024870</v>
+        <v>7024858</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,9 +983,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,22 +1010,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113187181</v>
+        <v>113187126</v>
       </c>
       <c r="B5" t="n">
-        <v>56781</v>
+        <v>90071</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,43 +1038,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685052</v>
+        <v>685103</v>
       </c>
       <c r="R5" t="n">
-        <v>7024833</v>
+        <v>7024817</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,19 +1096,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,22 +1113,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113186856</v>
+        <v>113187238</v>
       </c>
       <c r="B6" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685107</v>
+        <v>685022</v>
       </c>
       <c r="R6" t="n">
-        <v>7024929</v>
+        <v>7024825</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,19 +1199,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1216,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113186695</v>
+        <v>113189038</v>
       </c>
       <c r="B7" t="n">
-        <v>90485</v>
+        <v>97326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,24 +1244,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685137</v>
+        <v>685017</v>
       </c>
       <c r="R7" t="n">
-        <v>7024870</v>
+        <v>7024837</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,9 +1306,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,22 +1333,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188210</v>
+        <v>113189289</v>
       </c>
       <c r="B8" t="n">
-        <v>78121</v>
+        <v>90057</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,21 +1361,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,13 +1386,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>684969</v>
+        <v>685096</v>
       </c>
       <c r="R8" t="n">
-        <v>7024861</v>
+        <v>7024930</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,19 +1419,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,22 +1436,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113187010</v>
+        <v>113188942</v>
       </c>
       <c r="B9" t="n">
-        <v>56910</v>
+        <v>90021</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,47 +1460,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
+          <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685101</v>
+        <v>685000</v>
       </c>
       <c r="R9" t="n">
-        <v>7024816</v>
+        <v>7024832</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,19 +1522,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,22 +1539,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113187126</v>
+        <v>113189210</v>
       </c>
       <c r="B10" t="n">
-        <v>90059</v>
+        <v>90021</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,25 +1563,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685103</v>
+        <v>685061</v>
       </c>
       <c r="R10" t="n">
-        <v>7024817</v>
+        <v>7024867</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1664,22 +1642,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113189210</v>
+        <v>113189059</v>
       </c>
       <c r="B11" t="n">
-        <v>90009</v>
+        <v>90021</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685061</v>
+        <v>685035</v>
       </c>
       <c r="R11" t="n">
-        <v>7024867</v>
+        <v>7024859</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1779,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113189289</v>
+        <v>113186695</v>
       </c>
       <c r="B12" t="n">
-        <v>90045</v>
+        <v>90497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1791,25 +1769,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685096</v>
+        <v>685137</v>
       </c>
       <c r="R12" t="n">
-        <v>7024930</v>
+        <v>7024870</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1882,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113187338</v>
+        <v>113186700</v>
       </c>
       <c r="B13" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685080</v>
+        <v>685137</v>
       </c>
       <c r="R13" t="n">
-        <v>7024876</v>
+        <v>7024870</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1973,22 +1951,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113189038</v>
+        <v>113187255</v>
       </c>
       <c r="B14" t="n">
-        <v>97314</v>
+        <v>90497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,28 +1979,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2030,13 +2004,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685017</v>
+        <v>684984</v>
       </c>
       <c r="R14" t="n">
-        <v>7024837</v>
+        <v>7024863</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2063,19 +2037,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,22 +2054,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113189203</v>
+        <v>113187338</v>
       </c>
       <c r="B15" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,13 +2107,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685051</v>
+        <v>685080</v>
       </c>
       <c r="R15" t="n">
-        <v>7024861</v>
+        <v>7024876</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2176,19 +2140,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,22 +2157,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188942</v>
+        <v>113186856</v>
       </c>
       <c r="B16" t="n">
-        <v>90009</v>
+        <v>90057</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2227,25 +2181,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2256,13 +2210,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685000</v>
+        <v>685107</v>
       </c>
       <c r="R16" t="n">
-        <v>7024832</v>
+        <v>7024929</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2289,9 +2243,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,22 +2270,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113187373</v>
+        <v>113186913</v>
       </c>
       <c r="B17" t="n">
-        <v>90045</v>
+        <v>90071</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2334,21 +2298,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2359,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685080</v>
+        <v>685111</v>
       </c>
       <c r="R17" t="n">
-        <v>7024880</v>
+        <v>7024849</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2409,22 +2373,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188157</v>
+        <v>113189203</v>
       </c>
       <c r="B18" t="n">
-        <v>56781</v>
+        <v>90057</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2437,21 +2401,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,13 +2426,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684971</v>
+        <v>685051</v>
       </c>
       <c r="R18" t="n">
-        <v>7024844</v>
+        <v>7024861</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2495,9 +2459,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,22 +2486,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188009</v>
+        <v>113187373</v>
       </c>
       <c r="B19" t="n">
-        <v>97314</v>
+        <v>90057</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2536,32 +2510,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2569,13 +2539,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685000</v>
+        <v>685080</v>
       </c>
       <c r="R19" t="n">
-        <v>7024858</v>
+        <v>7024880</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2602,19 +2572,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,22 +2589,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113186913</v>
+        <v>113187010</v>
       </c>
       <c r="B20" t="n">
-        <v>90059</v>
+        <v>56911</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2657,38 +2617,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bredtomyran (Bredtomyran), Ång</t>
+          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685111</v>
+        <v>685101</v>
       </c>
       <c r="R20" t="n">
-        <v>7024849</v>
+        <v>7024816</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2715,9 +2680,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,22 +2707,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113187238</v>
+        <v>113188210</v>
       </c>
       <c r="B21" t="n">
-        <v>90045</v>
+        <v>78133</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,21 +2735,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2785,13 +2760,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685022</v>
+        <v>684969</v>
       </c>
       <c r="R21" t="n">
-        <v>7024825</v>
+        <v>7024861</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2818,9 +2793,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,22 +2820,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113189059</v>
+        <v>113188157</v>
       </c>
       <c r="B22" t="n">
-        <v>90009</v>
+        <v>56782</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2859,25 +2844,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2888,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685035</v>
+        <v>684971</v>
       </c>
       <c r="R22" t="n">
-        <v>7024859</v>
+        <v>7024844</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2950,10 +2935,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113187255</v>
+        <v>113187181</v>
       </c>
       <c r="B23" t="n">
-        <v>90485</v>
+        <v>56782</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,42 +2947,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684984</v>
+        <v>685052</v>
       </c>
       <c r="R23" t="n">
-        <v>7024863</v>
+        <v>7024833</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,9 +3014,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3056,7 +3056,7 @@
         <v>113187692</v>
       </c>
       <c r="B24" t="n">
-        <v>89991</v>
+        <v>90003</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113184262</v>
+        <v>113184104</v>
       </c>
       <c r="B2" t="n">
-        <v>90057</v>
+        <v>97326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -716,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685072</v>
+        <v>685031</v>
       </c>
       <c r="R2" t="n">
-        <v>7024868</v>
+        <v>7024817</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113184104</v>
+        <v>113184262</v>
       </c>
       <c r="B3" t="n">
-        <v>97326</v>
+        <v>90057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,32 +804,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685031</v>
+        <v>685072</v>
       </c>
       <c r="R3" t="n">
-        <v>7024817</v>
+        <v>7024868</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113187126</v>
+        <v>113186856</v>
       </c>
       <c r="B5" t="n">
-        <v>90071</v>
+        <v>90057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,21 +1038,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685103</v>
+        <v>685107</v>
       </c>
       <c r="R5" t="n">
-        <v>7024817</v>
+        <v>7024929</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,9 +1096,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,19 +1123,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113187238</v>
+        <v>113187373</v>
       </c>
       <c r="B6" t="n">
         <v>90057</v>
@@ -1166,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685022</v>
+        <v>685080</v>
       </c>
       <c r="R6" t="n">
-        <v>7024825</v>
+        <v>7024880</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1216,22 +1226,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113189038</v>
+        <v>113187238</v>
       </c>
       <c r="B7" t="n">
-        <v>97326</v>
+        <v>90057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,32 +1250,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1273,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685017</v>
+        <v>685022</v>
       </c>
       <c r="R7" t="n">
-        <v>7024837</v>
+        <v>7024825</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,19 +1312,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,19 +1329,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113189289</v>
+        <v>113187338</v>
       </c>
       <c r="B8" t="n">
         <v>90057</v>
@@ -1386,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685096</v>
+        <v>685080</v>
       </c>
       <c r="R8" t="n">
-        <v>7024930</v>
+        <v>7024876</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1436,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188942</v>
+        <v>113189203</v>
       </c>
       <c r="B9" t="n">
-        <v>90021</v>
+        <v>90057</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,25 +1456,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,13 +1485,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685000</v>
+        <v>685051</v>
       </c>
       <c r="R9" t="n">
-        <v>7024832</v>
+        <v>7024861</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,9 +1518,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,22 +1545,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113189210</v>
+        <v>113187255</v>
       </c>
       <c r="B10" t="n">
-        <v>90021</v>
+        <v>90497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,25 +1569,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685061</v>
+        <v>684984</v>
       </c>
       <c r="R10" t="n">
-        <v>7024867</v>
+        <v>7024863</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1654,7 +1660,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113189059</v>
+        <v>113188942</v>
       </c>
       <c r="B11" t="n">
         <v>90021</v>
@@ -1695,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685035</v>
+        <v>685000</v>
       </c>
       <c r="R11" t="n">
-        <v>7024859</v>
+        <v>7024832</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1745,22 +1751,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113186695</v>
+        <v>113187126</v>
       </c>
       <c r="B12" t="n">
-        <v>90497</v>
+        <v>90071</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,25 +1775,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685137</v>
+        <v>685103</v>
       </c>
       <c r="R12" t="n">
-        <v>7024870</v>
+        <v>7024817</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1848,22 +1854,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113186700</v>
+        <v>113189210</v>
       </c>
       <c r="B13" t="n">
-        <v>90057</v>
+        <v>90021</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,25 +1878,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685137</v>
+        <v>685061</v>
       </c>
       <c r="R13" t="n">
-        <v>7024870</v>
+        <v>7024867</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1963,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113187255</v>
+        <v>113188157</v>
       </c>
       <c r="B14" t="n">
-        <v>90497</v>
+        <v>56782</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,25 +1981,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>684984</v>
+        <v>684971</v>
       </c>
       <c r="R14" t="n">
-        <v>7024863</v>
+        <v>7024844</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2066,10 +2072,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113187338</v>
+        <v>113189059</v>
       </c>
       <c r="B15" t="n">
-        <v>90057</v>
+        <v>90021</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,25 +2084,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685080</v>
+        <v>685035</v>
       </c>
       <c r="R15" t="n">
-        <v>7024876</v>
+        <v>7024859</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2157,19 +2163,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113186856</v>
+        <v>113186700</v>
       </c>
       <c r="B16" t="n">
         <v>90057</v>
@@ -2210,13 +2216,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685107</v>
+        <v>685137</v>
       </c>
       <c r="R16" t="n">
-        <v>7024929</v>
+        <v>7024870</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,19 +2249,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,22 +2266,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113186913</v>
+        <v>113189289</v>
       </c>
       <c r="B17" t="n">
-        <v>90071</v>
+        <v>90057</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,21 +2294,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2323,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685111</v>
+        <v>685096</v>
       </c>
       <c r="R17" t="n">
-        <v>7024849</v>
+        <v>7024930</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2385,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113189203</v>
+        <v>113188210</v>
       </c>
       <c r="B18" t="n">
-        <v>90057</v>
+        <v>78133</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2401,21 +2397,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2426,7 +2422,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685051</v>
+        <v>684969</v>
       </c>
       <c r="R18" t="n">
         <v>7024861</v>
@@ -2461,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2471,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2486,22 +2482,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113187373</v>
+        <v>113186913</v>
       </c>
       <c r="B19" t="n">
-        <v>90057</v>
+        <v>90071</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2535,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685080</v>
+        <v>685111</v>
       </c>
       <c r="R19" t="n">
-        <v>7024880</v>
+        <v>7024849</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2589,12 +2585,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2719,10 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188210</v>
+        <v>113187181</v>
       </c>
       <c r="B21" t="n">
-        <v>78133</v>
+        <v>56782</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,35 +2731,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684969</v>
+        <v>685052</v>
       </c>
       <c r="R21" t="n">
-        <v>7024861</v>
+        <v>7024833</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2795,7 +2796,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2805,7 +2806,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,22 +2821,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188157</v>
+        <v>113189038</v>
       </c>
       <c r="B22" t="n">
-        <v>56782</v>
+        <v>97326</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2844,28 +2845,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2873,13 +2878,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684971</v>
+        <v>685017</v>
       </c>
       <c r="R22" t="n">
-        <v>7024844</v>
+        <v>7024837</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2906,9 +2911,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2923,22 +2938,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113187181</v>
+        <v>113186695</v>
       </c>
       <c r="B23" t="n">
-        <v>56782</v>
+        <v>90497</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2947,47 +2962,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685052</v>
+        <v>685137</v>
       </c>
       <c r="R23" t="n">
-        <v>7024833</v>
+        <v>7024870</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3014,19 +3024,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113187338</v>
+        <v>113188942</v>
       </c>
       <c r="B8" t="n">
-        <v>90057</v>
+        <v>90021</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685080</v>
+        <v>685000</v>
       </c>
       <c r="R8" t="n">
-        <v>7024876</v>
+        <v>7024832</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1444,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113189203</v>
+        <v>113187338</v>
       </c>
       <c r="B9" t="n">
         <v>90057</v>
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685051</v>
+        <v>685080</v>
       </c>
       <c r="R9" t="n">
-        <v>7024861</v>
+        <v>7024876</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1518,19 +1518,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,22 +1535,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113187255</v>
+        <v>113189203</v>
       </c>
       <c r="B10" t="n">
-        <v>90497</v>
+        <v>90057</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,25 +1559,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>684984</v>
+        <v>685051</v>
       </c>
       <c r="R10" t="n">
-        <v>7024863</v>
+        <v>7024861</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,9 +1621,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,22 +1648,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188942</v>
+        <v>113187255</v>
       </c>
       <c r="B11" t="n">
-        <v>90021</v>
+        <v>90497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,25 +1672,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685000</v>
+        <v>684984</v>
       </c>
       <c r="R11" t="n">
-        <v>7024832</v>
+        <v>7024863</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1751,12 +1751,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113187181</v>
+        <v>113186695</v>
       </c>
       <c r="B21" t="n">
-        <v>56782</v>
+        <v>90497</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,47 +2727,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685052</v>
+        <v>685137</v>
       </c>
       <c r="R21" t="n">
-        <v>7024833</v>
+        <v>7024870</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2794,19 +2789,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2821,22 +2806,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113189038</v>
+        <v>113187181</v>
       </c>
       <c r="B22" t="n">
-        <v>97326</v>
+        <v>56782</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2845,43 +2830,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685017</v>
+        <v>685052</v>
       </c>
       <c r="R22" t="n">
-        <v>7024837</v>
+        <v>7024833</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2913,7 +2899,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2909,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113186695</v>
+        <v>113189038</v>
       </c>
       <c r="B23" t="n">
-        <v>90497</v>
+        <v>97326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2966,24 +2952,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2991,13 +2981,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685137</v>
+        <v>685017</v>
       </c>
       <c r="R23" t="n">
-        <v>7024870</v>
+        <v>7024837</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3024,9 +3014,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113184104</v>
+        <v>113184262</v>
       </c>
       <c r="B2" t="n">
-        <v>97326</v>
+        <v>90079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -720,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685031</v>
+        <v>685072</v>
       </c>
       <c r="R2" t="n">
-        <v>7024817</v>
+        <v>7024868</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113184262</v>
+        <v>113184104</v>
       </c>
       <c r="B3" t="n">
-        <v>90057</v>
+        <v>97348</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,28 +800,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685072</v>
+        <v>685031</v>
       </c>
       <c r="R3" t="n">
-        <v>7024868</v>
+        <v>7024817</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188009</v>
+        <v>113188942</v>
       </c>
       <c r="B4" t="n">
-        <v>97326</v>
+        <v>90043</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,32 +917,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +949,10 @@
         <v>685000</v>
       </c>
       <c r="R4" t="n">
-        <v>7024858</v>
+        <v>7024832</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,19 +979,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,22 +996,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113186856</v>
+        <v>113186700</v>
       </c>
       <c r="B5" t="n">
-        <v>90057</v>
+        <v>90079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,13 +1049,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685107</v>
+        <v>685137</v>
       </c>
       <c r="R5" t="n">
-        <v>7024929</v>
+        <v>7024870</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,19 +1082,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,22 +1099,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113187373</v>
+        <v>113188210</v>
       </c>
       <c r="B6" t="n">
-        <v>90057</v>
+        <v>78155</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,13 +1152,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685080</v>
+        <v>684969</v>
       </c>
       <c r="R6" t="n">
-        <v>7024880</v>
+        <v>7024861</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,9 +1185,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,22 +1212,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113187238</v>
+        <v>113187181</v>
       </c>
       <c r="B7" t="n">
-        <v>90057</v>
+        <v>56782</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,38 +1240,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685022</v>
+        <v>685052</v>
       </c>
       <c r="R7" t="n">
-        <v>7024825</v>
+        <v>7024833</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,9 +1303,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,22 +1330,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188942</v>
+        <v>113187010</v>
       </c>
       <c r="B8" t="n">
-        <v>90021</v>
+        <v>56911</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,42 +1354,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bredtomyran (Bredtomyran), Ång</t>
+          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685000</v>
+        <v>685101</v>
       </c>
       <c r="R8" t="n">
-        <v>7024832</v>
+        <v>7024816</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,9 +1421,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,22 +1448,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113187338</v>
+        <v>113187238</v>
       </c>
       <c r="B9" t="n">
-        <v>90057</v>
+        <v>90079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685080</v>
+        <v>685022</v>
       </c>
       <c r="R9" t="n">
-        <v>7024876</v>
+        <v>7024825</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1535,22 +1551,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113189203</v>
+        <v>113188009</v>
       </c>
       <c r="B10" t="n">
-        <v>90057</v>
+        <v>97348</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,28 +1575,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1588,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685051</v>
+        <v>685000</v>
       </c>
       <c r="R10" t="n">
-        <v>7024861</v>
+        <v>7024858</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1623,7 +1643,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1653,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,22 +1668,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113187255</v>
+        <v>113187126</v>
       </c>
       <c r="B11" t="n">
-        <v>90497</v>
+        <v>90093</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,25 +1692,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>684984</v>
+        <v>685103</v>
       </c>
       <c r="R11" t="n">
-        <v>7024863</v>
+        <v>7024817</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1751,22 +1771,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113187126</v>
+        <v>113186695</v>
       </c>
       <c r="B12" t="n">
-        <v>90071</v>
+        <v>90519</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,25 +1795,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1824,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685103</v>
+        <v>685137</v>
       </c>
       <c r="R12" t="n">
-        <v>7024817</v>
+        <v>7024870</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1854,22 +1874,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113189210</v>
+        <v>113189203</v>
       </c>
       <c r="B13" t="n">
-        <v>90021</v>
+        <v>90079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,25 +1898,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,13 +1927,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685061</v>
+        <v>685051</v>
       </c>
       <c r="R13" t="n">
-        <v>7024867</v>
+        <v>7024861</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1940,9 +1960,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,22 +1987,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188157</v>
+        <v>113189289</v>
       </c>
       <c r="B14" t="n">
-        <v>56782</v>
+        <v>90079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,21 +2015,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>684971</v>
+        <v>685096</v>
       </c>
       <c r="R14" t="n">
-        <v>7024844</v>
+        <v>7024930</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2072,10 +2102,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113189059</v>
+        <v>113187255</v>
       </c>
       <c r="B15" t="n">
-        <v>90021</v>
+        <v>90519</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2084,25 +2114,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685035</v>
+        <v>684984</v>
       </c>
       <c r="R15" t="n">
-        <v>7024859</v>
+        <v>7024863</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2175,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113186700</v>
+        <v>113187373</v>
       </c>
       <c r="B16" t="n">
-        <v>90057</v>
+        <v>90079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2216,10 +2246,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685137</v>
+        <v>685080</v>
       </c>
       <c r="R16" t="n">
-        <v>7024870</v>
+        <v>7024880</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2266,22 +2296,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113189289</v>
+        <v>113189038</v>
       </c>
       <c r="B17" t="n">
-        <v>90057</v>
+        <v>97348</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,28 +2320,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2319,13 +2353,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685096</v>
+        <v>685017</v>
       </c>
       <c r="R17" t="n">
-        <v>7024930</v>
+        <v>7024837</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,9 +2386,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2369,22 +2413,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188210</v>
+        <v>113189210</v>
       </c>
       <c r="B18" t="n">
-        <v>78133</v>
+        <v>90043</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,25 +2437,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,13 +2466,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684969</v>
+        <v>685061</v>
       </c>
       <c r="R18" t="n">
-        <v>7024861</v>
+        <v>7024867</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2455,19 +2499,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,22 +2516,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113186913</v>
+        <v>113186856</v>
       </c>
       <c r="B19" t="n">
-        <v>90071</v>
+        <v>90079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,21 +2544,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2535,13 +2569,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685111</v>
+        <v>685107</v>
       </c>
       <c r="R19" t="n">
-        <v>7024849</v>
+        <v>7024929</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2568,9 +2602,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2585,22 +2629,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113187010</v>
+        <v>113186913</v>
       </c>
       <c r="B20" t="n">
-        <v>56911</v>
+        <v>90093</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2613,43 +2657,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
+          <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685101</v>
+        <v>685111</v>
       </c>
       <c r="R20" t="n">
-        <v>7024816</v>
+        <v>7024849</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2676,19 +2715,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,22 +2732,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113186695</v>
+        <v>113188157</v>
       </c>
       <c r="B21" t="n">
-        <v>90497</v>
+        <v>56782</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,25 +2756,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2756,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685137</v>
+        <v>684971</v>
       </c>
       <c r="R21" t="n">
-        <v>7024870</v>
+        <v>7024844</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2818,10 +2847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113187181</v>
+        <v>113189059</v>
       </c>
       <c r="B22" t="n">
-        <v>56782</v>
+        <v>90043</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2830,47 +2859,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685052</v>
+        <v>685035</v>
       </c>
       <c r="R22" t="n">
-        <v>7024833</v>
+        <v>7024859</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2897,19 +2921,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2924,22 +2938,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113189038</v>
+        <v>113187338</v>
       </c>
       <c r="B23" t="n">
-        <v>97326</v>
+        <v>90079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,32 +2962,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2981,13 +2991,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685017</v>
+        <v>685080</v>
       </c>
       <c r="R23" t="n">
-        <v>7024837</v>
+        <v>7024876</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3014,19 +3024,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3056,7 +3056,7 @@
         <v>113187692</v>
       </c>
       <c r="B24" t="n">
-        <v>90003</v>
+        <v>90025</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -2102,10 +2102,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113187255</v>
+        <v>113187373</v>
       </c>
       <c r="B15" t="n">
-        <v>90519</v>
+        <v>90079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2114,25 +2114,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>684984</v>
+        <v>685080</v>
       </c>
       <c r="R15" t="n">
-        <v>7024863</v>
+        <v>7024880</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2193,22 +2193,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113187373</v>
+        <v>113187255</v>
       </c>
       <c r="B16" t="n">
-        <v>90079</v>
+        <v>90519</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685080</v>
+        <v>684984</v>
       </c>
       <c r="R16" t="n">
-        <v>7024880</v>
+        <v>7024863</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2296,12 +2296,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113184262</v>
       </c>
       <c r="B2" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>113184104</v>
       </c>
       <c r="B3" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188942</v>
+        <v>113186695</v>
       </c>
       <c r="B4" t="n">
-        <v>90043</v>
+        <v>90523</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685000</v>
+        <v>685137</v>
       </c>
       <c r="R4" t="n">
-        <v>7024832</v>
+        <v>7024870</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -996,22 +996,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113186700</v>
+        <v>113189289</v>
       </c>
       <c r="B5" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685137</v>
+        <v>685096</v>
       </c>
       <c r="R5" t="n">
-        <v>7024870</v>
+        <v>7024930</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188210</v>
+        <v>113187255</v>
       </c>
       <c r="B6" t="n">
-        <v>78155</v>
+        <v>90523</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1123,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684969</v>
+        <v>684984</v>
       </c>
       <c r="R6" t="n">
-        <v>7024861</v>
+        <v>7024863</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,19 +1185,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,22 +1202,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113187181</v>
+        <v>113189203</v>
       </c>
       <c r="B7" t="n">
-        <v>56782</v>
+        <v>90083</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,40 +1230,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685052</v>
+        <v>685051</v>
       </c>
       <c r="R7" t="n">
-        <v>7024833</v>
+        <v>7024861</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1305,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,22 +1315,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113187010</v>
+        <v>113187373</v>
       </c>
       <c r="B8" t="n">
-        <v>56911</v>
+        <v>90083</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,43 +1343,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
+          <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685101</v>
+        <v>685080</v>
       </c>
       <c r="R8" t="n">
-        <v>7024816</v>
+        <v>7024880</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,19 +1401,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,22 +1418,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113187238</v>
+        <v>113188157</v>
       </c>
       <c r="B9" t="n">
-        <v>90079</v>
+        <v>56785</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,21 +1446,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685022</v>
+        <v>684971</v>
       </c>
       <c r="R9" t="n">
-        <v>7024825</v>
+        <v>7024844</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1563,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188009</v>
+        <v>113186856</v>
       </c>
       <c r="B10" t="n">
-        <v>97348</v>
+        <v>90083</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,32 +1545,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1608,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685000</v>
+        <v>685107</v>
       </c>
       <c r="R10" t="n">
-        <v>7024858</v>
+        <v>7024929</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1643,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1653,7 +1619,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,22 +1634,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113187126</v>
+        <v>113189038</v>
       </c>
       <c r="B11" t="n">
-        <v>90093</v>
+        <v>97352</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1692,28 +1658,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1721,13 +1691,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685103</v>
+        <v>685017</v>
       </c>
       <c r="R11" t="n">
-        <v>7024817</v>
+        <v>7024837</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1754,9 +1724,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,22 +1751,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113186695</v>
+        <v>113188210</v>
       </c>
       <c r="B12" t="n">
-        <v>90519</v>
+        <v>78158</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,25 +1775,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1824,13 +1804,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685137</v>
+        <v>684969</v>
       </c>
       <c r="R12" t="n">
-        <v>7024870</v>
+        <v>7024861</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,9 +1837,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,22 +1864,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113189203</v>
+        <v>113187238</v>
       </c>
       <c r="B13" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,13 +1917,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685051</v>
+        <v>685022</v>
       </c>
       <c r="R13" t="n">
-        <v>7024861</v>
+        <v>7024825</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1960,19 +1950,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,22 +1967,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113189289</v>
+        <v>113188942</v>
       </c>
       <c r="B14" t="n">
-        <v>90079</v>
+        <v>90047</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,25 +1991,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2040,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685096</v>
+        <v>685000</v>
       </c>
       <c r="R14" t="n">
-        <v>7024930</v>
+        <v>7024832</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2090,22 +2070,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113187373</v>
+        <v>113187010</v>
       </c>
       <c r="B15" t="n">
-        <v>90079</v>
+        <v>56914</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,38 +2098,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bredtomyran (Bredtomyran), Ång</t>
+          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685080</v>
+        <v>685101</v>
       </c>
       <c r="R15" t="n">
-        <v>7024880</v>
+        <v>7024816</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2176,9 +2161,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,22 +2188,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113187255</v>
+        <v>113188009</v>
       </c>
       <c r="B16" t="n">
-        <v>90519</v>
+        <v>97352</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,24 +2216,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2246,13 +2245,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>684984</v>
+        <v>685000</v>
       </c>
       <c r="R16" t="n">
-        <v>7024863</v>
+        <v>7024858</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2279,9 +2278,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2296,22 +2305,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113189038</v>
+        <v>113186913</v>
       </c>
       <c r="B17" t="n">
-        <v>97348</v>
+        <v>90097</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,32 +2329,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2353,13 +2358,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685017</v>
+        <v>685111</v>
       </c>
       <c r="R17" t="n">
-        <v>7024837</v>
+        <v>7024849</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2386,19 +2391,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,22 +2408,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113189210</v>
+        <v>113187338</v>
       </c>
       <c r="B18" t="n">
-        <v>90043</v>
+        <v>90083</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2437,25 +2432,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2466,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685061</v>
+        <v>685080</v>
       </c>
       <c r="R18" t="n">
-        <v>7024867</v>
+        <v>7024876</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2516,22 +2511,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113186856</v>
+        <v>113186700</v>
       </c>
       <c r="B19" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,13 +2564,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685107</v>
+        <v>685137</v>
       </c>
       <c r="R19" t="n">
-        <v>7024929</v>
+        <v>7024870</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2602,19 +2597,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,22 +2614,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113186913</v>
+        <v>113189059</v>
       </c>
       <c r="B20" t="n">
-        <v>90093</v>
+        <v>90047</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2653,25 +2638,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2682,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685111</v>
+        <v>685035</v>
       </c>
       <c r="R20" t="n">
-        <v>7024849</v>
+        <v>7024859</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2744,10 +2729,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188157</v>
+        <v>113187126</v>
       </c>
       <c r="B21" t="n">
-        <v>56782</v>
+        <v>90097</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,21 +2745,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2785,10 +2770,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684971</v>
+        <v>685103</v>
       </c>
       <c r="R21" t="n">
-        <v>7024844</v>
+        <v>7024817</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2835,22 +2820,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113189059</v>
+        <v>113187181</v>
       </c>
       <c r="B22" t="n">
-        <v>90043</v>
+        <v>56785</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2859,42 +2844,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685035</v>
+        <v>685052</v>
       </c>
       <c r="R22" t="n">
-        <v>7024859</v>
+        <v>7024833</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2921,9 +2911,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,22 +2938,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113187338</v>
+        <v>113189210</v>
       </c>
       <c r="B23" t="n">
-        <v>90079</v>
+        <v>90047</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,25 +2962,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685080</v>
+        <v>685061</v>
       </c>
       <c r="R23" t="n">
-        <v>7024876</v>
+        <v>7024867</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3041,12 +3041,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3056,7 +3056,7 @@
         <v>113187692</v>
       </c>
       <c r="B24" t="n">
-        <v>90025</v>
+        <v>90029</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188210</v>
+        <v>113187238</v>
       </c>
       <c r="B12" t="n">
-        <v>78158</v>
+        <v>90083</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,13 +1804,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684969</v>
+        <v>685022</v>
       </c>
       <c r="R12" t="n">
-        <v>7024861</v>
+        <v>7024825</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1837,19 +1837,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,22 +1854,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113187238</v>
+        <v>113188210</v>
       </c>
       <c r="B13" t="n">
-        <v>90083</v>
+        <v>78158</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,21 +1882,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685022</v>
+        <v>684969</v>
       </c>
       <c r="R13" t="n">
-        <v>7024825</v>
+        <v>7024861</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1950,9 +1940,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,22 +1967,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188942</v>
+        <v>113187010</v>
       </c>
       <c r="B14" t="n">
-        <v>90047</v>
+        <v>56914</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,42 +1991,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bredtomyran (Bredtomyran), Ång</t>
+          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685000</v>
+        <v>685101</v>
       </c>
       <c r="R14" t="n">
-        <v>7024832</v>
+        <v>7024816</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,9 +2058,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,22 +2085,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113187010</v>
+        <v>113188942</v>
       </c>
       <c r="B15" t="n">
-        <v>56914</v>
+        <v>90047</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,47 +2109,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
+          <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685101</v>
+        <v>685000</v>
       </c>
       <c r="R15" t="n">
-        <v>7024816</v>
+        <v>7024832</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2161,19 +2171,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,12 +2188,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113184262</v>
+        <v>113184104</v>
       </c>
       <c r="B2" t="n">
-        <v>90083</v>
+        <v>97352</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -716,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685072</v>
+        <v>685031</v>
       </c>
       <c r="R2" t="n">
-        <v>7024868</v>
+        <v>7024817</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22:17</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113184104</v>
+        <v>113184262</v>
       </c>
       <c r="B3" t="n">
-        <v>97352</v>
+        <v>90083</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,32 +804,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685031</v>
+        <v>685072</v>
       </c>
       <c r="R3" t="n">
-        <v>7024817</v>
+        <v>7024868</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113186695</v>
+        <v>113187010</v>
       </c>
       <c r="B4" t="n">
-        <v>90523</v>
+        <v>56918</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,42 +917,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bredtomyran (Bredtomyran), Ång</t>
+          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685137</v>
+        <v>685101</v>
       </c>
       <c r="R4" t="n">
-        <v>7024870</v>
+        <v>7024816</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,9 +984,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,22 +1011,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113189289</v>
+        <v>113187373</v>
       </c>
       <c r="B5" t="n">
-        <v>90083</v>
+        <v>90089</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685096</v>
+        <v>685080</v>
       </c>
       <c r="R5" t="n">
-        <v>7024930</v>
+        <v>7024880</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1099,22 +1114,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113187255</v>
+        <v>113186913</v>
       </c>
       <c r="B6" t="n">
-        <v>90523</v>
+        <v>90103</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1138,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684984</v>
+        <v>685111</v>
       </c>
       <c r="R6" t="n">
-        <v>7024863</v>
+        <v>7024849</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1214,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113189203</v>
+        <v>113188009</v>
       </c>
       <c r="B7" t="n">
-        <v>90083</v>
+        <v>97358</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,28 +1241,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685051</v>
+        <v>685000</v>
       </c>
       <c r="R7" t="n">
-        <v>7024861</v>
+        <v>7024858</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1290,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,22 +1334,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113187373</v>
+        <v>113189289</v>
       </c>
       <c r="B8" t="n">
-        <v>90083</v>
+        <v>90089</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685080</v>
+        <v>685096</v>
       </c>
       <c r="R8" t="n">
-        <v>7024880</v>
+        <v>7024930</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1418,22 +1437,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188157</v>
+        <v>113187255</v>
       </c>
       <c r="B9" t="n">
-        <v>56785</v>
+        <v>90529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,25 +1461,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684971</v>
+        <v>684984</v>
       </c>
       <c r="R9" t="n">
-        <v>7024844</v>
+        <v>7024863</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1533,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113186856</v>
+        <v>113187338</v>
       </c>
       <c r="B10" t="n">
-        <v>90083</v>
+        <v>90089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,13 +1593,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685107</v>
+        <v>685080</v>
       </c>
       <c r="R10" t="n">
-        <v>7024929</v>
+        <v>7024876</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1607,19 +1626,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,22 +1643,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113189038</v>
+        <v>113186700</v>
       </c>
       <c r="B11" t="n">
-        <v>97352</v>
+        <v>90089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,32 +1667,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1691,13 +1696,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685017</v>
+        <v>685137</v>
       </c>
       <c r="R11" t="n">
-        <v>7024837</v>
+        <v>7024870</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1724,19 +1729,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1751,22 +1746,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113187238</v>
+        <v>113189038</v>
       </c>
       <c r="B12" t="n">
-        <v>90083</v>
+        <v>97358</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,28 +1770,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1804,13 +1803,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685022</v>
+        <v>685017</v>
       </c>
       <c r="R12" t="n">
-        <v>7024825</v>
+        <v>7024837</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1837,9 +1836,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,22 +1863,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188210</v>
+        <v>113189203</v>
       </c>
       <c r="B13" t="n">
-        <v>78158</v>
+        <v>90089</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,21 +1891,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,7 +1916,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>684969</v>
+        <v>685051</v>
       </c>
       <c r="R13" t="n">
         <v>7024861</v>
@@ -1942,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,22 +1976,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Linnea Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113187010</v>
+        <v>113189210</v>
       </c>
       <c r="B14" t="n">
-        <v>56914</v>
+        <v>90053</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,47 +2000,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gullänget, Rundvägen (Gullänget, Rundvägen), Ång</t>
+          <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685101</v>
+        <v>685061</v>
       </c>
       <c r="R14" t="n">
-        <v>7024816</v>
+        <v>7024867</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2058,19 +2062,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,22 +2079,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188942</v>
+        <v>113186695</v>
       </c>
       <c r="B15" t="n">
-        <v>90047</v>
+        <v>90529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2109,25 +2103,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2138,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685000</v>
+        <v>685137</v>
       </c>
       <c r="R15" t="n">
-        <v>7024832</v>
+        <v>7024870</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2188,22 +2182,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188009</v>
+        <v>113188210</v>
       </c>
       <c r="B16" t="n">
-        <v>97352</v>
+        <v>78164</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2212,32 +2206,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2245,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685000</v>
+        <v>684969</v>
       </c>
       <c r="R16" t="n">
-        <v>7024858</v>
+        <v>7024861</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2280,7 +2270,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2290,7 +2280,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,22 +2295,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113186913</v>
+        <v>113188157</v>
       </c>
       <c r="B17" t="n">
-        <v>90097</v>
+        <v>56789</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,21 +2323,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2358,10 +2348,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685111</v>
+        <v>684971</v>
       </c>
       <c r="R17" t="n">
-        <v>7024849</v>
+        <v>7024844</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2420,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113187338</v>
+        <v>113187126</v>
       </c>
       <c r="B18" t="n">
-        <v>90083</v>
+        <v>90103</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2436,21 +2426,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2461,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685080</v>
+        <v>685103</v>
       </c>
       <c r="R18" t="n">
-        <v>7024876</v>
+        <v>7024817</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2523,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113186700</v>
+        <v>113187181</v>
       </c>
       <c r="B19" t="n">
-        <v>90083</v>
+        <v>56789</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2539,38 +2529,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685137</v>
+        <v>685052</v>
       </c>
       <c r="R19" t="n">
-        <v>7024870</v>
+        <v>7024833</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2597,9 +2592,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2614,22 +2619,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113189059</v>
+        <v>113187238</v>
       </c>
       <c r="B20" t="n">
-        <v>90047</v>
+        <v>90089</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2638,25 +2643,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2667,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685035</v>
+        <v>685022</v>
       </c>
       <c r="R20" t="n">
-        <v>7024859</v>
+        <v>7024825</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2729,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113187126</v>
+        <v>113189059</v>
       </c>
       <c r="B21" t="n">
-        <v>90097</v>
+        <v>90053</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,25 +2746,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2770,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685103</v>
+        <v>685035</v>
       </c>
       <c r="R21" t="n">
-        <v>7024817</v>
+        <v>7024859</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2820,22 +2825,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexander Elfving</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113187181</v>
+        <v>113186856</v>
       </c>
       <c r="B22" t="n">
-        <v>56785</v>
+        <v>90089</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2848,40 +2853,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bredtomyran (Bredtomyran), Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685052</v>
+        <v>685107</v>
       </c>
       <c r="R22" t="n">
-        <v>7024833</v>
+        <v>7024929</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,22 +2938,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113189210</v>
+        <v>113188942</v>
       </c>
       <c r="B23" t="n">
-        <v>90047</v>
+        <v>90053</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685061</v>
+        <v>685000</v>
       </c>
       <c r="R23" t="n">
-        <v>7024867</v>
+        <v>7024832</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3041,12 +3041,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Elfving</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188009</v>
+        <v>113189289</v>
       </c>
       <c r="B7" t="n">
-        <v>97358</v>
+        <v>90089</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,32 +1241,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1274,13 +1270,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685000</v>
+        <v>685096</v>
       </c>
       <c r="R7" t="n">
-        <v>7024858</v>
+        <v>7024930</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,19 +1303,9 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,22 +1320,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113189289</v>
+        <v>113187255</v>
       </c>
       <c r="B8" t="n">
-        <v>90089</v>
+        <v>90529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685096</v>
+        <v>684984</v>
       </c>
       <c r="R8" t="n">
-        <v>7024930</v>
+        <v>7024863</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1449,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113187255</v>
+        <v>113188009</v>
       </c>
       <c r="B9" t="n">
-        <v>90529</v>
+        <v>97358</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,24 +1451,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1490,13 +1480,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684984</v>
+        <v>685000</v>
       </c>
       <c r="R9" t="n">
-        <v>7024863</v>
+        <v>7024858</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,9 +1513,19 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,12 +1540,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -3056,7 +3056,7 @@
         <v>113187692</v>
       </c>
       <c r="B24" t="n">
-        <v>90029</v>
+        <v>90035</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -3056,7 +3056,7 @@
         <v>113187692</v>
       </c>
       <c r="B24" t="n">
-        <v>90035</v>
+        <v>90042</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 62089-2020 artfynd.xlsx
+++ b/artfynd/A 62089-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
